--- a/FOYER-ZERO-RECHERCHE.xlsx
+++ b/FOYER-ZERO-RECHERCHE.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F167B4D6-D552-2446-8087-77CF7B4C430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LISEZ-MOI" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="TA-OFFENSE" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="TA-DEFENSE" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="TA-SPECIAL" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="FOYER-ZERO" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="LISEZ-MOI" sheetId="1" r:id="rId1"/>
+    <sheet name="TA-OFFENSE" sheetId="2" r:id="rId2"/>
+    <sheet name="TA-DEFENSE" sheetId="3" r:id="rId3"/>
+    <sheet name="TA-SPECIAL" sheetId="4" r:id="rId4"/>
+    <sheet name="FOYER-ZERO" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,572 +35,594 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="183">
-  <si>
-    <t xml:space="preserve">Arbre de recherche — relevé TA et transposition Foyer Zéro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seize captures de l'écran RECHERCHE de Tiberium Alliances, onglets OFFENSE, DÉFENSE et SPÉCIAL,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relevées le 23/08/2026. Chaque carte donne un coût en crédits et un coût en points de recherche.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lecture des cellules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOIR        : valeur lue sur une capture.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUGE ITALIQUE sur fond rose : valeur ESTIMÉE. La recherche était déjà acquise ou hors capture,</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="191">
+  <si>
+    <t>Arbre de recherche — relevé TA et transposition Foyer Zéro</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Seize captures de l'écran RECHERCHE de Tiberium Alliances, onglets OFFENSE, DÉFENSE et SPÉCIAL,</t>
+  </si>
+  <si>
+    <t>relevées le 23/08/2026. Chaque carte donne un coût en crédits et un coût en points de recherche.</t>
+  </si>
+  <si>
+    <t>Lecture des cellules</t>
+  </si>
+  <si>
+    <t>NOIR        : valeur lue sur une capture.</t>
+  </si>
+  <si>
+    <t>ROUGE ITALIQUE sur fond rose : valeur ESTIMÉE. La recherche était déjà acquise ou hors capture,</t>
   </si>
   <si>
     <t xml:space="preserve">              le coût n'était donc pas affiché. À corriger.</t>
   </si>
   <si>
-    <t xml:space="preserve">JAUNE       : à remplir ou à trancher.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le rapport crédits / points de recherche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constant sur les 27 recherches lisibles : les points de recherche coûtent 2,0 à 2,6 fois les</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crédits, moyenne 2,4. La seule exception est le VCM, à 0,78 — c'est la recherche qui donne une</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base supplémentaire, elle ne suit pas le barème des unités.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foyer Zéro n'ayant pas de crédits, seule la colonne « points de recherche » est transposée.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le pas de l'arbre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaque échelon coûte environ le DOUBLE du précédent. Sur l'offense : 200k → 270k → 500k → 1,5M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ 5,8M → 9,85M → 19,6M → 42,5M → 100M → 120M. Sur la défense, treize échelons de 135k à 300M,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soit un rapport de 2 200 entre le premier et le dernier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ce que ça résout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le revenu en points de recherche DOUBLE par niveau de défense détruite. J'avais signalé que cela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">divergeait du ×1,32 de tout le reste. Les captures lèvent l'alerte : le COÛT de l'arbre double</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lui aussi à chaque échelon. Les deux courbes sont en phase, le ×2 est cohérent avec lui-même.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il reste à caler la cadence — combien de niveaux de progression pour un échelon d'arbre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les modules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ce sont des améliorations PERMANENTES, appliquées à toutes les unités du type concerné.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ils coûtent beaucoup plus cher que l'unité : le Fusilier est gratuit, son module vaut 10M.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quatre coûts seulement sont lisibles ; les autres n'apparaissent qu'une fois l'unité acquise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feuilles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA-OFFENSE · TA-DEFENSE · TA-SPECIAL : le relevé fidèle, avec les deux monnaies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOYER-ZERO : la transposition, avec nos noms et les points de recherche seuls.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA — onglet OFFENSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordre d'affichage dans le jeu, trois cartes par rangée. Les quatre premières étaient déjà acquises : coûts estimés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crédits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points de
+    <t>JAUNE       : à remplir ou à trancher.</t>
+  </si>
+  <si>
+    <t>Le rapport crédits / points de recherche</t>
+  </si>
+  <si>
+    <t>Constant sur les 27 recherches lisibles : les points de recherche coûtent 2,0 à 2,6 fois les</t>
+  </si>
+  <si>
+    <t>crédits, moyenne 2,4. La seule exception est le VCM, à 0,78 — c'est la recherche qui donne une</t>
+  </si>
+  <si>
+    <t>base supplémentaire, elle ne suit pas le barème des unités.</t>
+  </si>
+  <si>
+    <t>Foyer Zéro n'ayant pas de crédits, seule la colonne « points de recherche » est transposée.</t>
+  </si>
+  <si>
+    <t>Le pas de l'arbre</t>
+  </si>
+  <si>
+    <t>Chaque échelon coûte environ le DOUBLE du précédent. Sur l'offense : 200k → 270k → 500k → 1,5M</t>
+  </si>
+  <si>
+    <t>→ 5,8M → 9,85M → 19,6M → 42,5M → 100M → 120M. Sur la défense, treize échelons de 135k à 300M,</t>
+  </si>
+  <si>
+    <t>soit un rapport de 2 200 entre le premier et le dernier.</t>
+  </si>
+  <si>
+    <t>Ce que ça résout</t>
+  </si>
+  <si>
+    <t>Le revenu en points de recherche DOUBLE par niveau de défense détruite. J'avais signalé que cela</t>
+  </si>
+  <si>
+    <t>divergeait du ×1,32 de tout le reste. Les captures lèvent l'alerte : le COÛT de l'arbre double</t>
+  </si>
+  <si>
+    <t>lui aussi à chaque échelon. Les deux courbes sont en phase, le ×2 est cohérent avec lui-même.</t>
+  </si>
+  <si>
+    <t>Il reste à caler la cadence — combien de niveaux de progression pour un échelon d'arbre.</t>
+  </si>
+  <si>
+    <t>Les modules</t>
+  </si>
+  <si>
+    <t>Ce sont des améliorations PERMANENTES, appliquées à toutes les unités du type concerné.</t>
+  </si>
+  <si>
+    <t>Ils coûtent beaucoup plus cher que l'unité : le Fusilier est gratuit, son module vaut 10M.</t>
+  </si>
+  <si>
+    <t>Quatre coûts seulement sont lisibles ; les autres n'apparaissent qu'une fois l'unité acquise.</t>
+  </si>
+  <si>
+    <t>Feuilles</t>
+  </si>
+  <si>
+    <t>TA-OFFENSE · TA-DEFENSE · TA-SPECIAL : le relevé fidèle, avec les deux monnaies.</t>
+  </si>
+  <si>
+    <t>FOYER-ZERO : la transposition, avec nos noms et les points de recherche seuls.</t>
+  </si>
+  <si>
+    <t>TA — onglet OFFENSE</t>
+  </si>
+  <si>
+    <t>Ordre d'affichage dans le jeu, trois cartes par rangée. Les quatre premières étaient déjà acquises : coûts estimés.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Crédits</t>
+  </si>
+  <si>
+    <t>Points de
 recherche</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crédits
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Crédits
 module</t>
   </si>
   <si>
-    <t xml:space="preserve">Points rech.
+    <t>Points rech.
 module</t>
   </si>
   <si>
-    <t xml:space="preserve">Rifleman Squad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">escouade de base, contre l'infanterie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoke Grenade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">véhicule anti-infanterie rapide, courte portée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paladin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chasseur de véhicules volant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitbull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buggy rapide, fort impact sur les structures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flashbang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missile Squad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">envoyée contre les structures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missile Storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">char léger, contre les véhicules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAT-MP-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firehawk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frappe aérienne rapide contre les structures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nano Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone Troopers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">envoyés contre les véhicules ennemis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infanterie endurante spécialisée structures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tueur d'infanterie volant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juggernaut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">briseur de structures lent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sniper Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faible, mais surclasse l'infanterie en portée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laser Scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mammoth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">char lourd, gros dégâts, contre les véhicules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battering Ram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodiak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">briseur de structures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aegis Aura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA — onglet DÉFENSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mur et nid de mitrailleuse n'apparaissent pas dans l'arbre : ils sont disponibles d'emblée.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Défense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bloque, ne tire pas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gratuit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG Nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anti-infanterie de base, touche aussi le ciel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chasseur de véhicules mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infanterie anti-aérienne mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-Tank Barrier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure anti-véhicule, blesse au passage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repair Drones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">véhicule anti-infanterie rapide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardian Cannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tourelle lourde spécialisée véhicules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">véhicule anti-aérien rapide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbwire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure anti-infanterie, blesse infanterie et véhicules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">escouade anti-infanterie longue portée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tourelle lourde spécialisée aviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guided Missiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zone Trooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infanterie anti-véhicule mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watchtower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artillerie anti-infanterie, portée minimale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR Arms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titan Artillery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artillerie anti-véhicule, portée minimale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAM Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artillerie anti-aérienne, portée minimale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA — onglet SPÉCIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un seul soutien par base. Le VCM ouvre une base supplémentaire ; le second, à 1,2 trillion, correspond à la treizième.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rayon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ion Cannon Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soutien anti-véhicule, défend les bases alliées en alerte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falcon Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soutien anti-aérien, défend les bases alliées en alerte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skystrike Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soutien anti-infanterie — hors capture, estimé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCM (2e base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">permet de fonder une seconde base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCM (13e base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base supplémentaire de fin de partie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foyer Zéro — arbre de recherche transposé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points de recherche seuls : les crédits n'existent pas. Les coûts reprennent la colonne « points de recherche » de TA. La colonne « à retenir » est libre — c'est là que tu corriges.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom Foyer Zéro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Équivalent TA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coût TA
+    <t>Rifleman Squad</t>
+  </si>
+  <si>
+    <t>escouade de base, contre l'infanterie</t>
+  </si>
+  <si>
+    <t>Smoke Grenade</t>
+  </si>
+  <si>
+    <t>Guardian</t>
+  </si>
+  <si>
+    <t>véhicule anti-infanterie rapide, courte portée</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>chasseur de véhicules volant</t>
+  </si>
+  <si>
+    <t>Pitbull</t>
+  </si>
+  <si>
+    <t>buggy rapide, fort impact sur les structures</t>
+  </si>
+  <si>
+    <t>Flashbang</t>
+  </si>
+  <si>
+    <t>Missile Squad</t>
+  </si>
+  <si>
+    <t>envoyée contre les structures</t>
+  </si>
+  <si>
+    <t>Missile Storm</t>
+  </si>
+  <si>
+    <t>Predator</t>
+  </si>
+  <si>
+    <t>char léger, contre les véhicules</t>
+  </si>
+  <si>
+    <t>HEAT-MP-T</t>
+  </si>
+  <si>
+    <t>Firehawk</t>
+  </si>
+  <si>
+    <t>frappe aérienne rapide contre les structures</t>
+  </si>
+  <si>
+    <t>Nano Tech</t>
+  </si>
+  <si>
+    <t>Zone Troopers</t>
+  </si>
+  <si>
+    <t>envoyés contre les véhicules ennemis</t>
+  </si>
+  <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Commando</t>
+  </si>
+  <si>
+    <t>infanterie endurante spécialisée structures</t>
+  </si>
+  <si>
+    <t>Orca</t>
+  </si>
+  <si>
+    <t>tueur d'infanterie volant</t>
+  </si>
+  <si>
+    <t>EMP</t>
+  </si>
+  <si>
+    <t>Juggernaut</t>
+  </si>
+  <si>
+    <t>briseur de structures lent</t>
+  </si>
+  <si>
+    <t>Barrage</t>
+  </si>
+  <si>
+    <t>Sniper Team</t>
+  </si>
+  <si>
+    <t>faible, mais surclasse l'infanterie en portée</t>
+  </si>
+  <si>
+    <t>Laser Scope</t>
+  </si>
+  <si>
+    <t>Mammoth</t>
+  </si>
+  <si>
+    <t>char lourd, gros dégâts, contre les véhicules</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Kodiak</t>
+  </si>
+  <si>
+    <t>briseur de structures</t>
+  </si>
+  <si>
+    <t>Aegis Aura</t>
+  </si>
+  <si>
+    <t>TA — onglet DÉFENSE</t>
+  </si>
+  <si>
+    <t>Mur et nid de mitrailleuse n'apparaissent pas dans l'arbre : ils sont disponibles d'emblée.</t>
+  </si>
+  <si>
+    <t>Défense</t>
+  </si>
+  <si>
+    <t>Wall</t>
+  </si>
+  <si>
+    <t>bloque, ne tire pas</t>
+  </si>
+  <si>
+    <t>gratuit</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>MG Nest</t>
+  </si>
+  <si>
+    <t>anti-infanterie de base, touche aussi le ciel</t>
+  </si>
+  <si>
+    <t>chasseur de véhicules mobile</t>
+  </si>
+  <si>
+    <t>infanterie anti-aérienne mobile</t>
+  </si>
+  <si>
+    <t>Anti-Tank Barrier</t>
+  </si>
+  <si>
+    <t>structure anti-véhicule, blesse au passage</t>
+  </si>
+  <si>
+    <t>Repair Drones</t>
+  </si>
+  <si>
+    <t>véhicule anti-infanterie rapide</t>
+  </si>
+  <si>
+    <t>Guardian Cannon</t>
+  </si>
+  <si>
+    <t>tourelle lourde spécialisée véhicules</t>
+  </si>
+  <si>
+    <t>Garrison</t>
+  </si>
+  <si>
+    <t>véhicule anti-aérien rapide</t>
+  </si>
+  <si>
+    <t>Barbwire</t>
+  </si>
+  <si>
+    <t>structure anti-infanterie, blesse infanterie et véhicules</t>
+  </si>
+  <si>
+    <t>escouade anti-infanterie longue portée</t>
+  </si>
+  <si>
+    <t>Flak</t>
+  </si>
+  <si>
+    <t>tourelle lourde spécialisée aviation</t>
+  </si>
+  <si>
+    <t>Guided Missiles</t>
+  </si>
+  <si>
+    <t>Zone Trooper</t>
+  </si>
+  <si>
+    <t>infanterie anti-véhicule mobile</t>
+  </si>
+  <si>
+    <t>Watchtower</t>
+  </si>
+  <si>
+    <t>artillerie anti-infanterie, portée minimale</t>
+  </si>
+  <si>
+    <t>SR Arms</t>
+  </si>
+  <si>
+    <t>Titan Artillery</t>
+  </si>
+  <si>
+    <t>artillerie anti-véhicule, portée minimale</t>
+  </si>
+  <si>
+    <t>SAM Site</t>
+  </si>
+  <si>
+    <t>artillerie anti-aérienne, portée minimale</t>
+  </si>
+  <si>
+    <t>TA — onglet SPÉCIAL</t>
+  </si>
+  <si>
+    <t>Un seul soutien par base. Le VCM ouvre une base supplémentaire ; le second, à 1,2 trillion, correspond à la treizième.</t>
+  </si>
+  <si>
+    <t>Recherche</t>
+  </si>
+  <si>
+    <t>Rayon</t>
+  </si>
+  <si>
+    <t>Ion Cannon Support</t>
+  </si>
+  <si>
+    <t>soutien anti-véhicule, défend les bases alliées en alerte</t>
+  </si>
+  <si>
+    <t>Falcon Support</t>
+  </si>
+  <si>
+    <t>soutien anti-aérien, défend les bases alliées en alerte</t>
+  </si>
+  <si>
+    <t>Skystrike Support</t>
+  </si>
+  <si>
+    <t>soutien anti-infanterie — hors capture, estimé</t>
+  </si>
+  <si>
+    <t>VCM (2e base)</t>
+  </si>
+  <si>
+    <t>permet de fonder une seconde base</t>
+  </si>
+  <si>
+    <t>VCM (13e base)</t>
+  </si>
+  <si>
+    <t>base supplémentaire de fin de partie</t>
+  </si>
+  <si>
+    <t>Foyer Zéro — arbre de recherche transposé</t>
+  </si>
+  <si>
+    <t>Points de recherche seuls : les crédits n'existent pas. Les coûts reprennent la colonne « points de recherche » de TA. La colonne « à retenir » est libre — c'est là que tu corriges.</t>
+  </si>
+  <si>
+    <t>Branche</t>
+  </si>
+  <si>
+    <t>Nom Foyer Zéro</t>
+  </si>
+  <si>
+    <t>Équivalent TA</t>
+  </si>
+  <si>
+    <t>Coût TA
 (pts recherche)</t>
   </si>
   <si>
-    <t xml:space="preserve">À retenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coût module
+    <t>À retenir</t>
+  </si>
+  <si>
+    <t>Coût module
 TA</t>
   </si>
   <si>
-    <t xml:space="preserve">Offense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fusiliers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fumigène</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Éclaireur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garnison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épervier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pionnier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenadiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tir de barrage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chasseur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munition spéciale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foudre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camouflage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuirassiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sapeurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obusier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltigeurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percheron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Écraseur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albatros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouclier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merlon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-réparation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casemate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chasseur (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenadiers (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Éclaireur (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créneau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pionnier (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltigeurs (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Batterie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuirassiers (déf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faucheuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rayon mini −1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harpon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spécial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soutien anti-véh.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soutien anti-aérien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soutien anti-inf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deuxième base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCM</t>
+    <t>Offense</t>
+  </si>
+  <si>
+    <t>Fusiliers</t>
+  </si>
+  <si>
+    <t>Fumigène</t>
+  </si>
+  <si>
+    <t>Éclaireur</t>
+  </si>
+  <si>
+    <t>Garnison</t>
+  </si>
+  <si>
+    <t>Épervier</t>
+  </si>
+  <si>
+    <t>Pionnier</t>
+  </si>
+  <si>
+    <t>Grenadiers</t>
+  </si>
+  <si>
+    <t>Tir de barrage</t>
+  </si>
+  <si>
+    <t>Chasseur</t>
+  </si>
+  <si>
+    <t>Munition spéciale</t>
+  </si>
+  <si>
+    <t>Foudre</t>
+  </si>
+  <si>
+    <t>Camouflage</t>
+  </si>
+  <si>
+    <t>Cuirassiers</t>
+  </si>
+  <si>
+    <t>Booster</t>
+  </si>
+  <si>
+    <t>Sapeurs</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Obusier</t>
+  </si>
+  <si>
+    <t>Voltigeurs</t>
+  </si>
+  <si>
+    <t>Percheron</t>
+  </si>
+  <si>
+    <t>Écraseur</t>
+  </si>
+  <si>
+    <t>Albatros</t>
+  </si>
+  <si>
+    <t>Bouclier</t>
+  </si>
+  <si>
+    <t>Merlon</t>
+  </si>
+  <si>
+    <t>Auto-réparation</t>
+  </si>
+  <si>
+    <t>Casemate</t>
+  </si>
+  <si>
+    <t>Chasseur (déf)</t>
+  </si>
+  <si>
+    <t>Grenadiers (déf)</t>
+  </si>
+  <si>
+    <t>Herse</t>
+  </si>
+  <si>
+    <t>Éclaireur (déf)</t>
+  </si>
+  <si>
+    <t>Créneau</t>
+  </si>
+  <si>
+    <t>Pionnier (déf)</t>
+  </si>
+  <si>
+    <t>Ronce</t>
+  </si>
+  <si>
+    <t>Voltigeurs (déf)</t>
+  </si>
+  <si>
+    <t>Batterie</t>
+  </si>
+  <si>
+    <t>Cuirassiers (déf)</t>
+  </si>
+  <si>
+    <t>Faucheuse</t>
+  </si>
+  <si>
+    <t>Rayon mini −1</t>
+  </si>
+  <si>
+    <t>Mortier</t>
+  </si>
+  <si>
+    <t>Harpon</t>
+  </si>
+  <si>
+    <t>Spécial</t>
+  </si>
+  <si>
+    <t>Soutien anti-véh.</t>
+  </si>
+  <si>
+    <t>Soutien anti-aérien</t>
+  </si>
+  <si>
+    <t>Soutien anti-inf.</t>
+  </si>
+  <si>
+    <t>Deuxième base</t>
+  </si>
+  <si>
+    <t>VCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lisez moi pour claude de la part d'Ethan </t>
+  </si>
+  <si>
+    <t>j'ai trouvé une vidéo YouTube d'il y a 10 ans qui explique des trucs bref j'ai trouvé des valeurs pour les recherches modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pour le moment on ignore les bâtiments et mécanique de soutien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">le suivant </t>
+  </si>
+  <si>
+    <t>x2,5</t>
+  </si>
+  <si>
+    <t>apparition vers niv 25</t>
+  </si>
+  <si>
+    <t>apparition vers niv 30</t>
+  </si>
+  <si>
+    <t>apparition vers niv 35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,73 +631,57 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -695,16 +712,28 @@
         <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -720,105 +749,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -877,47 +861,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF404040"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -925,12 +925,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -959,7 +959,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -980,7 +980,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1031,7 +1031,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1049,236 +1049,242 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:B43"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col min="1" max="1" width="2.95703125" customWidth="1"/>
+    <col min="2" max="2" width="99.94921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" s="2"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" s="2"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>185</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
+    <col min="1" max="1" width="4.03515625" customWidth="1"/>
+    <col min="2" max="2" width="14.9296875" customWidth="1"/>
+    <col min="3" max="3" width="39.953125" customWidth="1"/>
+    <col min="4" max="5" width="13.046875" customWidth="1"/>
+    <col min="6" max="6" width="6.9921875" customWidth="1"/>
+    <col min="7" max="7" width="16.0078125" customWidth="1"/>
+    <col min="8" max="9" width="13.046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -1307,8 +1313,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1317,28 +1323,28 @@
       <c r="C5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="16">
         <v>0</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="16">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="str">
-        <f aca="false">IFERROR(E5/D5,"—")</f>
+        <f>IFERROR(E5/D5,"—")</f>
         <v>—</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="10">
         <v>5000000</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="10">
         <v>10000000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1347,28 +1353,28 @@
       <c r="C6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <f aca="false">IFERROR(E6/D6,"—")</f>
-        <v>2.5</v>
+      <c r="D6" s="16">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f>IFERROR(E6/D6,"—")</f>
+        <v>—</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="10">
         <v>30000000</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="10">
         <v>60000000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1377,28 +1383,28 @@
       <c r="C7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>36000</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <f aca="false">IFERROR(E7/D7,"—")</f>
-        <v>2.5</v>
+      <c r="D7" s="16">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f>IFERROR(E7/D7,"—")</f>
+        <v>—</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="10">
         <v>270000000</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="10">
         <v>540000000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1407,28 +1413,28 @@
       <c r="C8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <f aca="false">IFERROR(E8/D8,"—")</f>
-        <v>2.45454545454545</v>
+      <c r="D8" s="8">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="8">
+        <v>12500</v>
+      </c>
+      <c r="F8" s="9">
+        <f>IFERROR(E8/D8,"—")</f>
+        <v>2.5</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="10">
         <v>40000000</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="10">
         <v>80000000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1437,28 +1443,29 @@
       <c r="C9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="10">
         <v>80000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="10">
         <v>200000</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <f aca="false">IFERROR(E9/D9,"—")</f>
+      <c r="F9" s="9">
+        <f>IFERROR(E9/D9,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="8" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>120000000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="H9" s="16">
+        <f>I9/2</f>
+        <v>12000000</v>
+      </c>
+      <c r="I9" s="16">
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1467,28 +1474,29 @@
       <c r="C10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="10">
         <v>110000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>270000</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <f aca="false">IFERROR(E10/D10,"—")</f>
-        <v>2.45454545454545</v>
+      <c r="F10" s="9">
+        <f>IFERROR(E10/D10,"—")</f>
+        <v>2.4545454545454546</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>180000000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="H10" s="16">
+        <f t="shared" ref="H10:H18" si="0">I10/2</f>
+        <v>460000000</v>
+      </c>
+      <c r="I10" s="16">
+        <v>920000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1497,28 +1505,29 @@
       <c r="C11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="10">
         <v>200000</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="10">
         <v>500000</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <f aca="false">IFERROR(E11/D11,"—")</f>
+      <c r="F11" s="9">
+        <f>IFERROR(E11/D11,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>135000000</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>270000000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="H11" s="16">
+        <f t="shared" si="0"/>
+        <v>205000000</v>
+      </c>
+      <c r="I11" s="16">
+        <v>410000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1527,28 +1536,29 @@
       <c r="C12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="10">
         <v>600000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="10">
         <v>1500000</v>
       </c>
-      <c r="F12" s="9" t="n">
-        <f aca="false">IFERROR(E12/D12,"—")</f>
+      <c r="F12" s="9">
+        <f>IFERROR(E12/D12,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>400000000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="H12" s="16">
+        <f t="shared" si="0"/>
+        <v>5000000</v>
+      </c>
+      <c r="I12" s="16">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1557,28 +1567,29 @@
       <c r="C13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="10">
         <v>2400000</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="10">
         <v>5800000</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <f aca="false">IFERROR(E13/D13,"—")</f>
-        <v>2.41666666666667</v>
+      <c r="F13" s="9">
+        <f>IFERROR(E13/D13,"—")</f>
+        <v>2.4166666666666665</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="8" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>100000000</v>
+      </c>
+      <c r="I13" s="16">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1587,28 +1598,29 @@
       <c r="C14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="10">
         <v>4100000</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="10">
         <v>9850000</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <f aca="false">IFERROR(E14/D14,"—")</f>
-        <v>2.40243902439024</v>
+      <c r="F14" s="9">
+        <f>IFERROR(E14/D14,"—")</f>
+        <v>2.4024390243902438</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>900000000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="H14" s="16">
+        <f t="shared" si="0"/>
+        <v>75000000</v>
+      </c>
+      <c r="I14" s="16">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1617,28 +1629,29 @@
       <c r="C15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="10">
         <v>8650000</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="10">
         <v>19600000</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">IFERROR(E15/D15,"—")</f>
-        <v>2.26589595375723</v>
+      <c r="F15" s="9">
+        <f>IFERROR(E15/D15,"—")</f>
+        <v>2.2658959537572256</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>675000000</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>1350000000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="H15" s="16">
+        <f t="shared" si="0"/>
+        <v>500000000</v>
+      </c>
+      <c r="I15" s="16">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1647,28 +1660,29 @@
       <c r="C16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="10">
         <v>19000000</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="10">
         <v>42500000</v>
       </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">IFERROR(E16/D16,"—")</f>
-        <v>2.23684210526316</v>
+      <c r="F16" s="9">
+        <f>IFERROR(E16/D16,"—")</f>
+        <v>2.236842105263158</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="8" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>2000000000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>80000000</v>
+      </c>
+      <c r="I16" s="16">
+        <v>160000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1677,28 +1691,29 @@
       <c r="C17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="10">
         <v>40000000</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>100000000</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <f aca="false">IFERROR(E17/D17,"—")</f>
+      <c r="F17" s="9">
+        <f>IFERROR(E17/D17,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
         <v>1500000000</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="8">
         <v>3000000000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1707,64 +1722,59 @@
       <c r="C18" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="10">
         <v>60000000</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="10">
         <v>120000000</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <f aca="false">IFERROR(E18/D18,"—")</f>
+      <c r="F18" s="9">
+        <f>IFERROR(E18/D18,"—")</f>
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="8">
+        <f t="shared" si="0"/>
         <v>2250000000</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="8">
         <v>4500000000</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col min="1" max="1" width="4.03515625" customWidth="1"/>
+    <col min="2" max="2" width="17.75390625" customWidth="1"/>
+    <col min="3" max="3" width="41.96875" customWidth="1"/>
+    <col min="4" max="5" width="13.046875" customWidth="1"/>
+    <col min="6" max="6" width="6.9921875" customWidth="1"/>
+    <col min="7" max="7" width="16.94921875" customWidth="1"/>
+    <col min="8" max="8" width="13.71875" customWidth="1"/>
+    <col min="9" max="9" width="12.10546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -1786,9 +1796,15 @@
       <c r="G4" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="H4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1797,22 +1813,26 @@
       <c r="C5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="17" t="s">
         <v>86</v>
       </c>
       <c r="F5" s="9" t="str">
-        <f aca="false">IFERROR(E5/D5,"—")</f>
+        <f>IFERROR(E5/D5,"—")</f>
         <v>—</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="H5">
+        <f>I5/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1821,22 +1841,26 @@
       <c r="C6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="17" t="s">
         <v>86</v>
       </c>
       <c r="F6" s="9" t="str">
-        <f aca="false">IFERROR(E6/D6,"—")</f>
+        <f>IFERROR(E6/D6,"—")</f>
         <v>—</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="H6">
+        <f t="shared" ref="H6:H19" si="0">I6/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1845,22 +1869,29 @@
       <c r="C7" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="10">
         <v>55000</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="10">
         <v>135000</v>
       </c>
-      <c r="F7" s="9" t="n">
-        <f aca="false">IFERROR(E7/D7,"—")</f>
-        <v>2.45454545454545</v>
+      <c r="F7" s="9">
+        <f>IFERROR(E7/D7,"—")</f>
+        <v>2.4545454545454546</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>400000000</v>
+      </c>
+      <c r="I7">
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1869,22 +1900,29 @@
       <c r="C8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="10">
         <v>70000</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="10">
         <v>170000</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <f aca="false">IFERROR(E8/D8,"—")</f>
-        <v>2.42857142857143</v>
+      <c r="F8" s="9">
+        <f>IFERROR(E8/D8,"—")</f>
+        <v>2.4285714285714284</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>500000000</v>
+      </c>
+      <c r="I8">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1893,22 +1931,26 @@
       <c r="C9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="10">
         <v>80000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="10">
         <v>200000</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <f aca="false">IFERROR(E9/D9,"—")</f>
+      <c r="F9" s="9">
+        <f>IFERROR(E9/D9,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1917,22 +1959,29 @@
       <c r="C10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="10">
         <v>100000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>250000</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <f aca="false">IFERROR(E10/D10,"—")</f>
+      <c r="F10" s="9">
+        <f>IFERROR(E10/D10,"—")</f>
         <v>2.5</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>20000000</v>
+      </c>
+      <c r="I10">
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1941,22 +1990,29 @@
       <c r="C11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="10">
         <v>125000</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="10">
         <v>320000</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <f aca="false">IFERROR(E11/D11,"—")</f>
+      <c r="F11" s="9">
+        <f>IFERROR(E11/D11,"—")</f>
         <v>2.56</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>100000000</v>
+      </c>
+      <c r="I11">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1965,22 +2021,29 @@
       <c r="C12" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="10">
         <v>380000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="10">
         <v>940000</v>
       </c>
-      <c r="F12" s="9" t="n">
-        <f aca="false">IFERROR(E12/D12,"—")</f>
-        <v>2.47368421052632</v>
+      <c r="F12" s="9">
+        <f>IFERROR(E12/D12,"—")</f>
+        <v>2.4736842105263159</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>7000000</v>
+      </c>
+      <c r="I12">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1989,22 +2052,26 @@
       <c r="C13" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="10">
         <v>920000</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="10">
         <v>2200000</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <f aca="false">IFERROR(E13/D13,"—")</f>
-        <v>2.39130434782609</v>
+      <c r="F13" s="9">
+        <f>IFERROR(E13/D13,"—")</f>
+        <v>2.3913043478260869</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -2013,22 +2080,29 @@
       <c r="C14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="10">
         <v>2600000</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="10">
         <v>6200000</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <f aca="false">IFERROR(E14/D14,"—")</f>
-        <v>2.38461538461538</v>
+      <c r="F14" s="9">
+        <f>IFERROR(E14/D14,"—")</f>
+        <v>2.3846153846153846</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>550000000</v>
+      </c>
+      <c r="I14">
+        <v>1100000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -2037,22 +2111,26 @@
       <c r="C15" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="10">
         <v>5400000</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="10">
         <v>12300000</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">IFERROR(E15/D15,"—")</f>
-        <v>2.27777777777778</v>
+      <c r="F15" s="9">
+        <f>IFERROR(E15/D15,"—")</f>
+        <v>2.2777777777777777</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -2061,22 +2139,26 @@
       <c r="C16" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="10">
         <v>9500000</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="10">
         <v>21000000</v>
       </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">IFERROR(E16/D16,"—")</f>
-        <v>2.21052631578947</v>
+      <c r="F16" s="9">
+        <f>IFERROR(E16/D16,"—")</f>
+        <v>2.2105263157894739</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -2085,22 +2167,26 @@
       <c r="C17" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="10">
         <v>24000000</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>48000000</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <f aca="false">IFERROR(E17/D17,"—")</f>
+      <c r="F17" s="9">
+        <f>IFERROR(E17/D17,"—")</f>
         <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2109,22 +2195,26 @@
       <c r="C18" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="10">
         <v>50000000</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="10">
         <v>120000000</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <f aca="false">IFERROR(E18/D18,"—")</f>
+      <c r="F18" s="9">
+        <f>IFERROR(E18/D18,"—")</f>
         <v>2.4</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -2133,57 +2223,54 @@
       <c r="C19" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="10">
         <v>125000000</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>300000000</v>
       </c>
-      <c r="F19" s="9" t="n">
-        <f aca="false">IFERROR(E19/D19,"—")</f>
+      <c r="F19" s="9">
+        <f>IFERROR(E19/D19,"—")</f>
         <v>2.4</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>110</v>
       </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col min="1" max="1" width="23.9453125" customWidth="1"/>
+    <col min="2" max="2" width="46.00390625" customWidth="1"/>
+    <col min="3" max="3" width="14.9296875" customWidth="1"/>
+    <col min="4" max="4" width="20.984375" customWidth="1"/>
+    <col min="5" max="5" width="6.9921875" customWidth="1"/>
+    <col min="6" max="6" width="9.01171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>117</v>
       </c>
@@ -2203,146 +2290,138 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="10">
         <v>150000</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="10">
         <v>380000</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <f aca="false">IFERROR(D5/C5,"—")</f>
-        <v>2.53333333333333</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="9">
+        <f>IFERROR(D5/C5,"—")</f>
+        <v>2.5333333333333332</v>
+      </c>
+      <c r="F5" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>121</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="10">
         <v>460000</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="10">
         <v>1130000</v>
       </c>
-      <c r="E6" s="9" t="n">
-        <f aca="false">IFERROR(D6/C6,"—")</f>
-        <v>2.45652173913043</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="9">
+        <f>IFERROR(D6/C6,"—")</f>
+        <v>2.4565217391304346</v>
+      </c>
+      <c r="F6" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>123</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="8">
         <v>1000000</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="8">
         <v>2500000</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <f aca="false">IFERROR(D7/C7,"—")</f>
+      <c r="E7" s="9">
+        <f>IFERROR(D7/C7,"—")</f>
         <v>2.5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>125</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="10">
         <v>1800000</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="10">
         <v>1400000</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">IFERROR(D8/C8,"—")</f>
-        <v>0.777777777777778</v>
+      <c r="E8" s="9">
+        <f>IFERROR(D8/C8,"—")</f>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>127</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="10">
         <v>2000000000000</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="10">
         <v>1200000000000</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <f aca="false">IFERROR(D9/C9,"—")</f>
+      <c r="E9" s="9">
+        <f>IFERROR(D9/C9,"—")</f>
         <v>0.6</v>
       </c>
       <c r="F9" s="6"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col min="1" max="1" width="11.02734375" customWidth="1"/>
+    <col min="2" max="3" width="16.94921875" customWidth="1"/>
+    <col min="4" max="4" width="14.9296875" customWidth="1"/>
+    <col min="5" max="5" width="13.046875" customWidth="1"/>
+    <col min="6" max="6" width="16.94921875" customWidth="1"/>
+    <col min="7" max="7" width="14.9296875" customWidth="1"/>
+    <col min="8" max="8" width="13.046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>131</v>
       </c>
@@ -2368,19 +2447,19 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>137</v>
       </c>
@@ -2390,19 +2469,26 @@
       <c r="C6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="10">
+        <f>'TA-OFFENSE'!E5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
       <c r="F6" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="10">
+        <f>'TA-OFFENSE'!I5</f>
         <v>10000000</v>
       </c>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="18">
+        <f>G6</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>137</v>
       </c>
@@ -2412,19 +2498,26 @@
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E7" s="15"/>
+      <c r="D7" s="10">
+        <f>'TA-OFFENSE'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
       <c r="F7" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="10">
+        <f>'TA-OFFENSE'!I6</f>
         <v>60000000</v>
       </c>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="18">
+        <f t="shared" ref="H7:H10" si="0">G7</f>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>137</v>
       </c>
@@ -2434,19 +2527,26 @@
       <c r="C8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E8" s="15"/>
+      <c r="D8" s="10">
+        <f>'TA-OFFENSE'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>50000</v>
+      </c>
       <c r="F8" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="10">
+        <f>'TA-OFFENSE'!I7</f>
         <v>540000000</v>
       </c>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="18">
+        <f t="shared" si="0"/>
+        <v>540000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>137</v>
       </c>
@@ -2456,19 +2556,26 @@
       <c r="C9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>135000</v>
-      </c>
-      <c r="E9" s="15"/>
+      <c r="D9" s="10">
+        <f>'TA-OFFENSE'!E8</f>
+        <v>12500</v>
+      </c>
+      <c r="E9" s="14">
+        <v>12500</v>
+      </c>
       <c r="F9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="10">
+        <f>'TA-OFFENSE'!I8</f>
         <v>80000000</v>
       </c>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="18">
+        <f t="shared" si="0"/>
+        <v>80000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>137</v>
       </c>
@@ -2478,19 +2585,26 @@
       <c r="C10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="10">
+        <f>'TA-OFFENSE'!E9</f>
         <v>200000</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="14">
+        <v>200000</v>
+      </c>
       <c r="F10" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="10">
+        <f>'TA-OFFENSE'!I9</f>
+        <v>24000000</v>
+      </c>
+      <c r="H10" s="18">
+        <f t="shared" si="0"/>
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>137</v>
       </c>
@@ -2500,19 +2614,25 @@
       <c r="C11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="10">
+        <f>'TA-OFFENSE'!E10</f>
         <v>270000</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="14">
+        <v>300000</v>
+      </c>
       <c r="F11" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>180000000</v>
-      </c>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G11" s="10">
+        <f>'TA-OFFENSE'!I10</f>
+        <v>920000000</v>
+      </c>
+      <c r="H11" s="18">
+        <v>300000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>137</v>
       </c>
@@ -2522,19 +2642,25 @@
       <c r="C12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="10">
+        <f>'TA-OFFENSE'!E11</f>
         <v>500000</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="14">
+        <v>750000</v>
+      </c>
       <c r="F12" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>270000000</v>
-      </c>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G12" s="10">
+        <f>'TA-OFFENSE'!I11</f>
+        <v>410000000</v>
+      </c>
+      <c r="H12" s="18">
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>137</v>
       </c>
@@ -2544,19 +2670,26 @@
       <c r="C13" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="10">
+        <f>'TA-OFFENSE'!E12</f>
         <v>1500000</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="18">
+        <f>D13</f>
+        <v>1500000</v>
+      </c>
       <c r="F13" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="10">
+        <f>'TA-OFFENSE'!I12</f>
+        <v>10000000</v>
+      </c>
+      <c r="H13" s="18">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>137</v>
       </c>
@@ -2566,19 +2699,26 @@
       <c r="C14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="10">
+        <f>'TA-OFFENSE'!E13</f>
         <v>5800000</v>
       </c>
-      <c r="E14" s="15"/>
+      <c r="E14" s="18">
+        <f t="shared" ref="E14:E19" si="1">D14</f>
+        <v>5800000</v>
+      </c>
       <c r="F14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>600000000</v>
-      </c>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="10">
+        <f>'TA-OFFENSE'!I13</f>
+        <v>200000000</v>
+      </c>
+      <c r="H14" s="18">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>137</v>
       </c>
@@ -2588,19 +2728,26 @@
       <c r="C15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="10">
+        <f>'TA-OFFENSE'!E14</f>
         <v>9850000</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="18">
+        <f t="shared" si="1"/>
+        <v>9850000</v>
+      </c>
       <c r="F15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>900000000</v>
-      </c>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G15" s="10">
+        <f>'TA-OFFENSE'!I14</f>
+        <v>150000000</v>
+      </c>
+      <c r="H15" s="18">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>137</v>
       </c>
@@ -2610,19 +2757,26 @@
       <c r="C16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="10">
+        <f>'TA-OFFENSE'!E15</f>
         <v>19600000</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="18">
+        <f t="shared" si="1"/>
+        <v>19600000</v>
+      </c>
       <c r="F16" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>1350000000</v>
-      </c>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="10">
+        <f>'TA-OFFENSE'!I15</f>
+        <v>1000000000</v>
+      </c>
+      <c r="H16" s="18">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>137</v>
       </c>
@@ -2632,19 +2786,26 @@
       <c r="C17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="10">
+        <f>'TA-OFFENSE'!E16</f>
         <v>42500000</v>
       </c>
-      <c r="E17" s="15"/>
+      <c r="E17" s="18">
+        <f t="shared" si="1"/>
+        <v>42500000</v>
+      </c>
       <c r="F17" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>2000000000</v>
-      </c>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G17" s="10">
+        <f>'TA-OFFENSE'!I16</f>
+        <v>160000000</v>
+      </c>
+      <c r="H17" s="18">
+        <v>1200000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>137</v>
       </c>
@@ -2654,19 +2815,26 @@
       <c r="C18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="10">
+        <f>'TA-OFFENSE'!E17</f>
         <v>100000000</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E18" s="18">
+        <f t="shared" si="1"/>
+        <v>100000000</v>
+      </c>
       <c r="F18" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="10">
+        <f>'TA-OFFENSE'!I17</f>
         <v>3000000000</v>
       </c>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="18">
+        <v>1500000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>137</v>
       </c>
@@ -2676,31 +2844,38 @@
       <c r="C19" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="10">
+        <f>'TA-OFFENSE'!E18</f>
         <v>120000000</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="18">
+        <f t="shared" si="1"/>
+        <v>120000000</v>
+      </c>
       <c r="F19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="10">
+        <f>'TA-OFFENSE'!I18</f>
         <v>4500000000</v>
       </c>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="H19" s="18">
+        <v>2500000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>83</v>
       </c>
@@ -2710,17 +2885,26 @@
       <c r="C21" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15"/>
+      <c r="D21" s="10" t="str">
+        <f>'TA-DEFENSE'!E5</f>
+        <v>gratuit</v>
+      </c>
+      <c r="E21" s="18" t="str">
+        <f>D21</f>
+        <v>gratuit</v>
+      </c>
       <c r="F21" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G21" s="10">
+        <f>'TA-DEFENSE'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="18">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>83</v>
       </c>
@@ -2730,17 +2914,26 @@
       <c r="C22" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15"/>
+      <c r="D22" s="10" t="str">
+        <f>'TA-DEFENSE'!E6</f>
+        <v>gratuit</v>
+      </c>
+      <c r="E22" s="18" t="str">
+        <f t="shared" ref="E22:E35" si="2">D22</f>
+        <v>gratuit</v>
+      </c>
       <c r="F22" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G22" s="10">
+        <f>'TA-DEFENSE'!I6</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <v>140000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>83</v>
       </c>
@@ -2750,17 +2943,27 @@
       <c r="C23" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="10">
+        <f>'TA-DEFENSE'!E7</f>
         <v>135000</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="18">
+        <f t="shared" si="2"/>
+        <v>135000</v>
+      </c>
       <c r="F23" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G23" s="10">
+        <f>'TA-DEFENSE'!I7</f>
+        <v>800000000</v>
+      </c>
+      <c r="H23" s="18">
+        <f t="shared" ref="H22:H35" si="3">G23</f>
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>83</v>
       </c>
@@ -2770,17 +2973,26 @@
       <c r="C24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="10">
+        <f>'TA-DEFENSE'!E8</f>
         <v>170000</v>
       </c>
-      <c r="E24" s="15"/>
+      <c r="E24" s="18">
+        <f t="shared" si="2"/>
+        <v>170000</v>
+      </c>
       <c r="F24" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G24" s="10">
+        <f>'TA-DEFENSE'!I8</f>
+        <v>1000000000</v>
+      </c>
+      <c r="H24" s="18">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>83</v>
       </c>
@@ -2790,17 +3002,26 @@
       <c r="C25" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="10">
+        <f>'TA-DEFENSE'!E9</f>
         <v>200000</v>
       </c>
-      <c r="E25" s="15"/>
+      <c r="E25" s="18">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
       <c r="F25" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G25" s="10">
+        <f>'TA-DEFENSE'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="18">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>83</v>
       </c>
@@ -2810,17 +3031,27 @@
       <c r="C26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="10">
+        <f>'TA-DEFENSE'!E10</f>
         <v>250000</v>
       </c>
-      <c r="E26" s="15"/>
+      <c r="E26" s="18">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
       <c r="F26" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G26" s="10">
+        <f>'TA-DEFENSE'!I10</f>
+        <v>40000000</v>
+      </c>
+      <c r="H26" s="18">
+        <f t="shared" si="3"/>
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>83</v>
       </c>
@@ -2830,17 +3061,27 @@
       <c r="C27" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="10">
+        <f>'TA-DEFENSE'!E11</f>
         <v>320000</v>
       </c>
-      <c r="E27" s="15"/>
+      <c r="E27" s="18">
+        <f t="shared" si="2"/>
+        <v>320000</v>
+      </c>
       <c r="F27" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G27" s="10">
+        <f>'TA-DEFENSE'!I11</f>
+        <v>200000000</v>
+      </c>
+      <c r="H27" s="18">
+        <f t="shared" si="3"/>
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>83</v>
       </c>
@@ -2850,17 +3091,27 @@
       <c r="C28" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="10">
+        <f>'TA-DEFENSE'!E12</f>
         <v>940000</v>
       </c>
-      <c r="E28" s="15"/>
+      <c r="E28" s="18">
+        <f t="shared" si="2"/>
+        <v>940000</v>
+      </c>
       <c r="F28" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G28" s="10">
+        <f>'TA-DEFENSE'!I12</f>
+        <v>14000000</v>
+      </c>
+      <c r="H28" s="18">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>83</v>
       </c>
@@ -2870,17 +3121,26 @@
       <c r="C29" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="10">
+        <f>'TA-DEFENSE'!E13</f>
         <v>2200000</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="18">
+        <f t="shared" si="2"/>
+        <v>2200000</v>
+      </c>
       <c r="F29" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G29" s="10">
+        <f>'TA-DEFENSE'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="18">
+        <v>80000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>83</v>
       </c>
@@ -2890,17 +3150,27 @@
       <c r="C30" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="10">
+        <f>'TA-DEFENSE'!E14</f>
         <v>6200000</v>
       </c>
-      <c r="E30" s="15"/>
+      <c r="E30" s="18">
+        <f t="shared" si="2"/>
+        <v>6200000</v>
+      </c>
       <c r="F30" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G30" s="10">
+        <f>'TA-DEFENSE'!I14</f>
+        <v>1100000000</v>
+      </c>
+      <c r="H30" s="18">
+        <f t="shared" si="3"/>
+        <v>1100000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>83</v>
       </c>
@@ -2910,17 +3180,26 @@
       <c r="C31" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="10">
+        <f>'TA-DEFENSE'!E15</f>
         <v>12300000</v>
       </c>
-      <c r="E31" s="15"/>
+      <c r="E31" s="18">
+        <f t="shared" si="2"/>
+        <v>12300000</v>
+      </c>
       <c r="F31" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G31" s="10">
+        <f>'TA-DEFENSE'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="18">
+        <v>450000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>83</v>
       </c>
@@ -2930,17 +3209,26 @@
       <c r="C32" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="10">
+        <f>'TA-DEFENSE'!E16</f>
         <v>21000000</v>
       </c>
-      <c r="E32" s="15"/>
+      <c r="E32" s="18">
+        <f t="shared" si="2"/>
+        <v>21000000</v>
+      </c>
       <c r="F32" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G32" s="10">
+        <f>'TA-DEFENSE'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="18">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>83</v>
       </c>
@@ -2950,17 +3238,26 @@
       <c r="C33" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="10">
+        <f>'TA-DEFENSE'!E17</f>
         <v>48000000</v>
       </c>
-      <c r="E33" s="15"/>
+      <c r="E33" s="18">
+        <f t="shared" si="2"/>
+        <v>48000000</v>
+      </c>
       <c r="F33" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G33" s="10">
+        <f>'TA-DEFENSE'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>900000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>83</v>
       </c>
@@ -2970,17 +3267,26 @@
       <c r="C34" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="10">
+        <f>'TA-DEFENSE'!E18</f>
         <v>120000000</v>
       </c>
-      <c r="E34" s="15"/>
+      <c r="E34" s="18">
+        <f t="shared" si="2"/>
+        <v>120000000</v>
+      </c>
       <c r="F34" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G34" s="10">
+        <f>'TA-DEFENSE'!I18</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="18">
+        <v>1400000000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>83</v>
       </c>
@@ -2990,29 +3296,38 @@
       <c r="C35" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D35" s="10">
+        <f>'TA-DEFENSE'!E19</f>
         <v>300000000</v>
       </c>
-      <c r="E35" s="15"/>
+      <c r="E35" s="18">
+        <f t="shared" si="2"/>
+        <v>300000000</v>
+      </c>
       <c r="F35" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="G35" s="10">
+        <f>'TA-DEFENSE'!I19</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="18">
+        <v>2000000000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>177</v>
       </c>
@@ -3022,17 +3337,19 @@
       <c r="C37" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="10">
         <v>380000</v>
       </c>
-      <c r="E37" s="15"/>
+      <c r="E37" s="19" t="s">
+        <v>188</v>
+      </c>
       <c r="F37" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G37" s="10"/>
-      <c r="H37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>177</v>
       </c>
@@ -3042,17 +3359,19 @@
       <c r="C38" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="10">
         <v>1130000</v>
       </c>
-      <c r="E38" s="15"/>
+      <c r="E38" s="19" t="s">
+        <v>190</v>
+      </c>
       <c r="F38" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G38" s="10"/>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>177</v>
       </c>
@@ -3062,17 +3381,19 @@
       <c r="C39" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="10">
         <v>2500000</v>
       </c>
-      <c r="E39" s="15"/>
+      <c r="E39" s="19" t="s">
+        <v>189</v>
+      </c>
       <c r="F39" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G39" s="10"/>
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>177</v>
       </c>
@@ -3082,23 +3403,28 @@
       <c r="C40" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="10">
         <v>1400000</v>
       </c>
-      <c r="E40" s="15"/>
+      <c r="E40" s="19">
+        <v>2000000</v>
+      </c>
       <c r="F40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G40" s="10"/>
-      <c r="H40" s="15"/>
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" t="s">
+        <v>187</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>